--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_706_Somalia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_706_Somalia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R66a8483bedde47d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8fa719b1913540c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R65a6711db55a47a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb133282830314e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3ac1c7f6d55d485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc04cbc221c054859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3443aeafc0fd447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R67de64285e3d4f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra2049b1a148445f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcf9f8a7ad3d5479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf8cc38704597466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R11d84226e5a54fdf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ706CommercialTable" displayName="EEZ706CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ706CommercialTable" displayName="EEZ706CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ706FunctionalTable" displayName="EEZ706FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ706FunctionalTable" displayName="EEZ706FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ706ValidationTable" displayName="EEZ706ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ706ValidationTable" displayName="EEZ706ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8801,7 +8755,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda8bbc7ef6664b29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11900bdae8324b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8811,20 +8765,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8832,606 +8776,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2228.3801518469995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.200114536152961</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.53112302577046</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2228.3801518469995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.5386408396</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$122,A2,'Species'!$U$2:$U$122))</x:f>
-        <x:v>353284.36054776475</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.200114536152961</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.53112302577046</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>353267.60800064175</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>16.75254712300375</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000047421690366</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00004742169036616943</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2848.9116871757</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0624954269198854</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>115.47698250076127</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2848.9116871757</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>146.32129095092992</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$122,A3,'Species'!$U$2:$U$122))</x:f>
-        <x:v>416856.4358727403</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0624954269198854</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>115.47698250076127</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>328983.7250462026</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>87872.71082653769</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2671035195257663</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2671035195257662</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2.8463614352999995</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6462166500598103</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>442.80921495246224</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2.8463614352999995</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1067.0400207248022</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$122,A4,'Species'!$U$2:$U$122))</x:f>
-        <x:v>3037.1815649127893</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6462166500598103</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>442.80921495246224</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1260.3950726361563</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1776.786492276633</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.4097059968351253</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.4097059968351253</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3094.4487127294997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.719196448529794</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>52.38373352978026</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3094.4487127294997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>143.15085267383117</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$122,A5,'Species'!$U$2:$U$122))</x:f>
-        <x:v>442972.9717826671</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.719196448529794</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>52.38373352978026</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>162098.77678919365</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>280874.1949934735</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.732734821057564</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.732734821057564</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.2961508898</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0961538461668336</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.478254705073377</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.2961508898</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.489667421434033</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$122,A6,'Species'!$U$2:$U$122))</x:f>
-        <x:v>3.6988261201637602</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0961538461668336</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.478254705073377</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3.695446234058517</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.0033798861052432017</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0009146083831753</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0009146083831752162</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>23617.910401775</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4275153877519666</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>267.6180412895626</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>23617.910401775</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>317.7167789203428</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$122,A7,'Species'!$U$2:$U$122))</x:f>
-        <x:v>7503806.417681213</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4275153877519666</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>267.6180412895626</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6320578.921075412</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1183227.4966058005</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1872023925942026</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.18720239259420254</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>66646.5636295951</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.861376722653516</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>726.7360811143511</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>66646.5636295951</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1147.3408543640755</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$122,A8,'Species'!$U$2:$U$122))</x:f>
-        <x:v>76466325.25520936</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.861376722653516</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>726.7360811143511</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>48434462.471910186</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>28031862.78329917</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5787586225315577</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5787586225315579</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>131.4344888025</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8999999999999995</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242805</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>131.4344888025</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$122,A9,'Species'!$U$2:$U$122))</x:f>
-        <x:v>104402.12547237815</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8999999999999995</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242805</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>104402.12547237803</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.1641532182693481e-10</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.1150665879664984e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>27329.7123225263</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.136526715021921</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1369.3886218397406</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>27329.7123225263</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1649.4459956462474</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$122,A10,'Species'!$U$2:$U$122))</x:f>
-        <x:v>45078884.552554905</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.136526715021921</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1369.3886218397406</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>37424997.092620865</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7653887.459934041</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2045127068678696</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.20451270686786954</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>13803.3052765067</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.408465901688617</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2561.3321550853852</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>13803.3052765067</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2582.397516638148</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$122,A11,'Species'!$U$2:$U$122))</x:f>
-        <x:v>35645621.26744915</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.408465901688617</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2561.3321550853852</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>35354849.65117638</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>290771.61627276987</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0082243771120971</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.008224377112097121</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ba8abc45e084501"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R940c5063218a4afc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9441,20 +8991,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9462,1200 +9002,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3682.0774805747</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.775743236076896</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>596.6824112388632</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3682.0774805747</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>625.6648013092444</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$122,A2,'Species'!$U$2:$U$122))</x:f>
-        <x:v>2303746.2752890126</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.775743236076896</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>596.6824112388632</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2197030.8694776306</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>106715.40581138199</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0485725563959667</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.048572556395966714</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>7732.4503007503</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4524951342429</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>283.4621874719174</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>7732.4503007503</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>286.39575215249516</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$122,A3,'Species'!$U$2:$U$122))</x:f>
-        <x:v>2214540.9198651696</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4524951342429</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>283.4621874719174</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2191857.2767685656</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>22683.64309660392</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0103490511617828</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.01034905116178285</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>308.5258260476</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.258225475978976</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1812.2807440338781</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>308.5258260476</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1974.2799871282402</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$122,A4,'Species'!$U$2:$U$122))</x:f>
-        <x:v>609116.3638779854</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.258225475978976</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1812.2807440338781</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>559135.4135832114</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>49980.950294774026</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0893897061079925</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08938970610799236</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>18.0077584388</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9433548939618066</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>877.7177759128757</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>18.0077584388</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1171.3982005177695</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$122,A5,'Species'!$U$2:$U$122))</x:f>
-        <x:v>21094.255830569</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9433548939618066</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>877.7177759128757</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>15805.729686079854</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5288.526144489146</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3345955074220182</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3345955074220182</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>20180.623195310898</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.467425499092202</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2933.76618880548</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>20180.623195310898</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2949.5953387237723</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$122,A6,'Species'!$U$2:$U$122))</x:f>
-        <x:v>59524672.109429866</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.467425499092202</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2933.76618880548</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>59205229.99942672</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>319442.11000314355</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.005395504924248</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.005395504924248021</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4166.4079641384005</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7198091230400863</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.5768525716479</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4166.4079641384005</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.6215807828144</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$122,A7,'Species'!$U$2:$U$122))</x:f>
-        <x:v>2185787.532332395</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7198091230400863</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.5768525716479</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2185601.1763571696</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>186.35597522556782</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000852653161252</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00008526531612513812</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>798.867195555</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.28</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1905.4607179632483</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>798.867195555</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1905.4607179632483</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$122,A8,'Species'!$U$2:$U$122))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1522210.059999517</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.28</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1905.4607179632483</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>1522210.059999517</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>23163.3043583879</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.211482147423386</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1627.3544184842353</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>23163.3043583879</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1851.7693484733775</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$122,A9,'Species'!$U$2:$U$122))</x:f>
-        <x:v>42893097.02022251</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.211482147423386</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1627.3544184842353</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>37694905.6943177</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5198191.325904809</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1379016933497306</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1379016933497305</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1159.1914641170001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.7663984077582797</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>58.39805835833143</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1159.1914641170001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>77.00497042340736</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$122,A10,'Species'!$U$2:$U$122))</x:f>
-        <x:v>89263.50440939587</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.7663984077582797</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>58.39805835833143</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>67694.53076998422</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>21568.973639411648</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.318622101284663</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.318622101284663</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>435.15172605500004</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>435.15172605500004</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$122,A11,'Species'!$U$2:$U$122))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>996875.0132654638</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>996875.0132654638</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>344.15123870810004</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2667898052520012</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>184.8373805625798</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>344.15123870810004</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>200.98345094280052</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$122,A12,'Species'!$U$2:$U$122))</x:f>
-        <x:v>69168.70360179346</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2667898052520012</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>184.8373805625798</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>63612.01348017233</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>5556.690121621126</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0873528413520999</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.08735284135209978</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>19826.672751748403</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4993000053625556</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>315.71848152544</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>19826.672751748403</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>409.8126034355122</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$122,A13,'Species'!$U$2:$U$122))</x:f>
-        <x:v>8125220.377857944</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4993000053625556</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>315.71848152544</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>6259647.014883823</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1865573.3629741212</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2980317194465232</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.29803171944652307</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>28096.4752625931</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.980853285674127</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>956.8707644821992</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>28096.4752625931</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1261.148826866997</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$122,A14,'Species'!$U$2:$U$122))</x:f>
-        <x:v>35433836.81651689</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.980853285674127</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>956.8707644821992</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>26884695.76377266</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>8549141.052744232</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3179928509462349</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.3179928509462349</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>13395.347877549299</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6133219731352195</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>410.5083289827254</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>13395.347877549299</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>509.03183831504157</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$122,A15,'Species'!$U$2:$U$122))</x:f>
-        <x:v>6818658.55497841</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6133219731352195</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>410.5083289827254</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5498901.87335506</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1319756.68162335</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2400036792833553</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.2400036792833554</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>51.8547423199</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.4280933501722166</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>26.797442651453384</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>51.8547423199</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>26.8329606247375</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$122,A16,'Species'!$U$2:$U$122))</x:f>
-        <x:v>1391.4162588757858</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.4280933501722166</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>26.797442651453384</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1389.574483523413</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1.8417753523729061</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0013254239871352</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0013254239871351768</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1689.7202230587002</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.26562558567558</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>184.34254783917865</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1689.7202230587002</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>193.87406683832057</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$122,A17,'Species'!$U$2:$U$122))</x:f>
-        <x:v>327592.9314633444</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.26562558567558</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>184.34254783917865</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>311487.3310540261</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>16105.600409318286</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0517054750022075</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.05170547500220753</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4623.6229006551</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4623.6229006551</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$122,A18,'Species'!$U$2:$U$122))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>803493.5708583028</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>803493.5708583028</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>4606.7045065704</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.5118013881287378</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>324.9386622135239</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>4606.7045065704</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>325.15400670391097</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$122,A19,'Species'!$U$2:$U$122))</x:f>
-        <x:v>1497888.4280123285</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.5118013881287378</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>324.9386622135239</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1496896.3995779974</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>992.0284343310632</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0006627235088619</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.000662723508861892</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>5145.8426264791</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.8766418141857213</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>75.27344873866335</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>5145.8426264791</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>100.70769388584412</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$122,A20,'Species'!$U$2:$U$122))</x:f>
-        <x:v>518225.94401218527</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.8766418141857213</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>75.27344873866335</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>387345.32116150326</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>130880.622850682</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.3378913225496571</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.33789132254965704</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>275.9634227899</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.306484138218224</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>202.52756361249868</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>275.9634227899</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>203.93024099120154</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$122,A21,'Species'!$U$2:$U$122))</x:f>
-        <x:v>56277.287314301146</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.306484138218224</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>202.52756361249868</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>55890.19966380434</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>387.0876504968037</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0069258591457044</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.006925859145704389</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2.8463614352999995</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.6462166500598103</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>442.80921495246224</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2.8463614352999995</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>1067.0400207248022</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$122,A22,'Species'!$U$2:$U$122))</x:f>
-        <x:v>3037.1815649127893</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.6462166500598103</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>442.80921495246224</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1260.3950726361563</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1776.786492276633</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>2.4097059968351253</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>1.4097059968351253</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R238344f119d44175"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcc527040d244b26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10830,7 +9591,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10929,7 +9690,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>166015194.26696122</x:v>
+        <x:v>128484904.46261014</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10943,7 +9704,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>166015194.26696122</x:v>
+        <x:v>148400965.22101557</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10957,7 +9718,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-37530289.80435108</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10971,7 +9732,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-17614229.045945644</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10982,9 +9743,9 @@
         <x:v>EEZ_706</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10996,47 +9757,19 @@
         <x:v>EEZ_706</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_706</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_706</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90335f83951f4c31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7695a8be63034262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11083,7 +9816,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
